--- a/engagement_survey_forms/036_leadership_network_feedback--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/036_leadership_network_feedback--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'moderately_agree'}</t>
+          <t>moderately_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Moderately agree'}</t>
+          <t>Moderately agree</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'weakly_agree'}</t>
+          <t>weakly_agree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Weakly agree'}</t>
+          <t>Weakly agree</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'frequently_attend'}</t>
+          <t>frequently_attend</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Frequently attend'}</t>
+          <t>Frequently attend</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally_attend'}</t>
+          <t>occasionally_attend</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionally attend'}</t>
+          <t>Occasionally attend</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'rarely_attend'}</t>
+          <t>rarely_attend</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely attend'}</t>
+          <t>Rarely attend</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'never_attend'}</t>
+          <t>never_attend</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Never attend'}</t>
+          <t>Never attend</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'moderately_agree'}</t>
+          <t>moderately_agree</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Moderately agree'}</t>
+          <t>Moderately agree</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'weakly_agree'}</t>
+          <t>weakly_agree</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Weakly agree'}</t>
+          <t>Weakly agree</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
